--- a/Training/Day3_Calibration/matlab_pipeline/data/output/IO_2019_5sec_for_DGE_IO_Data.xlsx
+++ b/Training/Day3_Calibration/matlab_pipeline/data/output/IO_2019_5sec_for_DGE_IO_Data.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="IO_Data_Replacement" sheetId="1" r:id="rId2"/>
+    <sheet name="IO_Data_Replacement" sheetId="2" r:id="rId3"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="25" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
   <si>
     <t>Intermediate Input Shares and Sectoral Accounts (phiQI, phiX, phiM_I, phiW, phiY0, phiN0)</t>
   </si>
@@ -42,10 +43,34 @@
     <t>Subsector</t>
   </si>
   <si>
+    <t>Primary</t>
+  </si>
+  <si>
     <t>Fossil</t>
   </si>
   <si>
     <t>Renewables</t>
+  </si>
+  <si>
+    <t>Secondary</t>
+  </si>
+  <si>
+    <t>Tertiary</t>
+  </si>
+  <si>
+    <t>Primary</t>
+  </si>
+  <si>
+    <t>Fossil</t>
+  </si>
+  <si>
+    <t>Renewables</t>
+  </si>
+  <si>
+    <t>Secondary</t>
+  </si>
+  <si>
+    <t>Tertiary</t>
   </si>
   <si>
     <t>Exports (phiX)</t>
@@ -66,7 +91,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fonts count="1">
     <font>
       <sz val="11"/>
@@ -104,23 +129,23 @@
 </styleSheet>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="80.7109375" customWidth="true"/>
-    <col min="2" max="2" width="12" customWidth="true"/>
+    <col min="1" max="1" width="73.48828125" customWidth="true"/>
+    <col min="2" max="2" width="10.93359375" customWidth="true"/>
     <col min="3" max="3" width="15.7109375" customWidth="true"/>
     <col min="4" max="4" width="14.7109375" customWidth="true"/>
     <col min="5" max="5" width="15.7109375" customWidth="true"/>
     <col min="6" max="6" width="15.7109375" customWidth="true"/>
     <col min="7" max="7" width="15.7109375" customWidth="true"/>
-    <col min="8" max="8" width="15.5703125" customWidth="true"/>
-    <col min="9" max="9" width="28.140625" customWidth="true"/>
+    <col min="8" max="8" width="15.37890625" customWidth="true"/>
+    <col min="9" max="9" width="25.7109375" customWidth="true"/>
     <col min="10" max="10" width="15.7109375" customWidth="true"/>
-    <col min="11" max="11" width="19.28515625" customWidth="true"/>
-    <col min="12" max="12" width="25" customWidth="true"/>
+    <col min="11" max="11" width="17.26953125" customWidth="true"/>
+    <col min="12" max="12" width="22.7109375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -147,34 +172,34 @@
         <v>8</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="I2" s="0" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J2" s="0" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="K2" s="0" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="L2" s="0" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
@@ -198,7 +223,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C4" s="0">
         <v>0.014422226930467616</v>
@@ -236,7 +261,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5" s="0">
         <v>0.00064131046250132996</v>
@@ -274,7 +299,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" s="0">
         <v>1.2809840480249971e-05</v>
@@ -298,7 +323,7 @@
         <v>0.00035363100675160186</v>
       </c>
       <c r="J6" s="0">
-        <v>0.00072204021226881621</v>
+        <v>0.0007220402122688162</v>
       </c>
       <c r="K6" s="0">
         <v>0.0033232510115607959</v>
@@ -312,7 +337,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C7" s="0">
         <v>0.068289060727302633</v>
@@ -350,7 +375,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C8" s="0">
         <v>0.0058979093180920004</v>
@@ -362,10 +387,10 @@
         <v>0.0015030145154121396</v>
       </c>
       <c r="F8" s="0">
-        <v>0.037154401221751531</v>
+        <v>0.03715440122175153</v>
       </c>
       <c r="G8" s="0">
-        <v>0.050678527879484806</v>
+        <v>0.050678527879484805</v>
       </c>
       <c r="H8" s="0">
         <v>0.033650860704118872</v>
